--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.151.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.151.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.151" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.22250.151" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.151.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.151.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0151.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0151.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.151.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.151.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.22250.151" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.151" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,18 +422,18 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="41" customWidth="1" min="14" max="14"/>
-    <col width="40" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -611,18 +611,18 @@
           <t>L6: suspicious token(s): 6wer (letter/digit mix) | candidate OCR token mismatch vs other OCR: "swer" vs "6wer" :: to be still fur- 6wer in the old form, will be done away with to a greater</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>L43: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” that is, how may the case be resisted by affidavits, and</t>
-        </is>
-      </c>
+      <c r="J2" s="1" t="inlineStr"/>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L31: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: onlyâ€”namelj</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]144</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]144</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L1: isolated marker/symbol line :: 144</t>
@@ -630,7 +630,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L70: isolated marker/symbol line :: &gt;</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]144</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -661,7 +661,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>87</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -674,16 +674,8 @@
         </is>
       </c>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L49: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: spoken of as being â€œso wide in its language that it in</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>L32: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: a claim,â€”tha</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
+      <c r="K3" s="1" t="inlineStr"/>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
@@ -693,7 +685,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L72: isolated marker/symbol line :: /</t>
+          <t>L70: isolated marker/symbol line :: &gt;</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -729,16 +721,8 @@
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L69: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: onlyâ€”namely</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L86: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”that is, how far may the case he resisted by affidavits, and</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
@@ -748,7 +732,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L103: isolated marker/symbol line :: 1</t>
+          <t>L72: isolated marker/symbol line :: /</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -770,12 +754,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -784,11 +768,7 @@
       <c r="G5" s="1" t="inlineStr"/>
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L72: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: a claim,â€” tha</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
       <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
@@ -799,7 +779,7 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L105: isolated marker/symbol line :: N</t>
+          <t>L103: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -835,11 +815,7 @@
       <c r="G6" s="1" t="inlineStr"/>
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>L126: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” that is, how may the case be resisted by affidavits, and</t>
-        </is>
-      </c>
+      <c r="J6" s="1" t="inlineStr"/>
       <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
@@ -848,7 +824,11 @@
           <t>L127: isolated marker/symbol line :: 2</t>
         </is>
       </c>
-      <c r="O6" s="1" t="inlineStr"/>
+      <c r="O6" s="1" t="inlineStr">
+        <is>
+          <t>L105: isolated marker/symbol line :: N</t>
+        </is>
+      </c>
       <c r="P6" s="1" t="inlineStr"/>
       <c r="Q6" s="1" t="inlineStr"/>
       <c r="R6" s="1" t="inlineStr"/>
@@ -882,11 +862,7 @@
       <c r="G7" s="1" t="inlineStr"/>
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>L137: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: spoken of as being â€œso wide in its language that it in</t>
-        </is>
-      </c>
+      <c r="J7" s="1" t="inlineStr"/>
       <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
@@ -993,12 +969,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1037,7 +1013,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1076,7 +1052,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
